--- a/aligned.xlsx
+++ b/aligned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,205 +459,240 @@
           <t>Line_5</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Line_6</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2945.309397721254</v>
+        <v>12.21101387668025</v>
       </c>
       <c r="C2" t="n">
-        <v>43016.67860263007</v>
+        <v>159.9583738044581</v>
       </c>
       <c r="D2" t="n">
-        <v>80619.23175511241</v>
+        <v>145.759803339482</v>
       </c>
       <c r="E2" t="n">
-        <v>13282.8968114429</v>
+        <v>247.9251519432211</v>
       </c>
       <c r="F2" t="n">
-        <v>68827.17198142297</v>
+        <v>38.22696172506139</v>
+      </c>
+      <c r="G2" t="n">
+        <v>130.1872620167249</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.2945</v>
+        <v>0.2015</v>
       </c>
       <c r="B3" t="n">
-        <v>2599.130121268797</v>
+        <v>15.94287236113902</v>
       </c>
       <c r="C3" t="n">
-        <v>44781.52065646918</v>
+        <v>209.8273032595552</v>
       </c>
       <c r="D3" t="n">
-        <v>80255.54399165053</v>
+        <v>160.946422111699</v>
       </c>
       <c r="E3" t="n">
-        <v>13076.07013305702</v>
+        <v>273.8117638848835</v>
       </c>
       <c r="F3" t="n">
-        <v>66593.01712164856</v>
+        <v>37.24076451610355</v>
+      </c>
+      <c r="G3" t="n">
+        <v>146.3375685862185</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.6045</v>
+        <v>0.403</v>
       </c>
       <c r="B4" t="n">
-        <v>2174.751798759332</v>
+        <v>16.01289249425934</v>
       </c>
       <c r="C4" t="n">
-        <v>41436.54074230355</v>
+        <v>232.2420713895919</v>
       </c>
       <c r="D4" t="n">
-        <v>72616.37560611151</v>
+        <v>160.2019482270446</v>
       </c>
       <c r="E4" t="n">
-        <v>12203.75719762043</v>
+        <v>266.8232819346197</v>
       </c>
       <c r="F4" t="n">
-        <v>60176.43833977688</v>
+        <v>35.35064294353376</v>
+      </c>
+      <c r="G4" t="n">
+        <v>145.5711408250891</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.9145</v>
+        <v>0.6045</v>
       </c>
       <c r="B5" t="n">
-        <v>1691.05816107243</v>
+        <v>14.1728147989769</v>
       </c>
       <c r="C5" t="n">
-        <v>34504.90170117926</v>
+        <v>231.847406715758</v>
       </c>
       <c r="D5" t="n">
-        <v>59131.99575873774</v>
+        <v>139.8963887663711</v>
       </c>
       <c r="E5" t="n">
-        <v>10292.65077815989</v>
+        <v>236.4770463056933</v>
       </c>
       <c r="F5" t="n">
-        <v>50723.54794898017</v>
+        <v>31.41299862151702</v>
+      </c>
+      <c r="G5" t="n">
+        <v>135.9412858492883</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1.2245</v>
+        <v>0.806</v>
       </c>
       <c r="B6" t="n">
-        <v>1212.318035772963</v>
+        <v>11.38055463533234</v>
       </c>
       <c r="C6" t="n">
-        <v>26708.57070665681</v>
+        <v>212.4863095839963</v>
       </c>
       <c r="D6" t="n">
-        <v>45062.4782096446</v>
+        <v>117.2023352813611</v>
       </c>
       <c r="E6" t="n">
-        <v>8272.152506118497</v>
+        <v>198.2008842201856</v>
       </c>
       <c r="F6" t="n">
-        <v>40288.18575218721</v>
+        <v>26.49417358710955</v>
+      </c>
+      <c r="G6" t="n">
+        <v>121.6626366487313</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.5345</v>
+        <v>1.0075</v>
       </c>
       <c r="B7" t="n">
-        <v>799.5104997734074</v>
+        <v>8.360234556651175</v>
       </c>
       <c r="C7" t="n">
-        <v>18809.42634353658</v>
+        <v>185.2359609983585</v>
       </c>
       <c r="D7" t="n">
-        <v>31816.80003886235</v>
+        <v>91.32741218562043</v>
       </c>
       <c r="E7" t="n">
-        <v>6243.204767089796</v>
+        <v>157.2088416511988</v>
       </c>
       <c r="F7" t="n">
-        <v>30199.44846974994</v>
+        <v>21.42435278934765</v>
+      </c>
+      <c r="G7" t="n">
+        <v>104.0243980599022</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1.8445</v>
+        <v>1.209</v>
       </c>
       <c r="B8" t="n">
-        <v>484.9012618380088</v>
+        <v>5.64194417360033</v>
       </c>
       <c r="C8" t="n">
-        <v>12164.0346365964</v>
+        <v>154.7829156001911</v>
       </c>
       <c r="D8" t="n">
-        <v>20639.5260873824</v>
+        <v>66.04928816684884</v>
       </c>
       <c r="E8" t="n">
-        <v>4282.605617023029</v>
+        <v>113.7847043672635</v>
       </c>
       <c r="F8" t="n">
-        <v>20891.75530450091</v>
+        <v>16.74058245734086</v>
+      </c>
+      <c r="G8" t="n">
+        <v>83.327889583184</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2.1545</v>
+        <v>1.4105</v>
       </c>
       <c r="B9" t="n">
-        <v>270.9203492734052</v>
+        <v>3.513065511582063</v>
       </c>
       <c r="C9" t="n">
-        <v>7225.716634800476</v>
+        <v>125.2082246551783</v>
       </c>
       <c r="D9" t="n">
-        <v>12174.25484871203</v>
+        <v>45.74081887298403</v>
       </c>
       <c r="E9" t="n">
-        <v>2860.268487108638</v>
+        <v>76.60863904782903</v>
       </c>
       <c r="F9" t="n">
-        <v>13347.57080550057</v>
+        <v>12.53652444565592</v>
+      </c>
+      <c r="G9" t="n">
+        <v>64.95158945530336</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2.4645</v>
+        <v>1.612</v>
       </c>
       <c r="B10" t="n">
-        <v>138.86099986545</v>
+        <v>2.00716841768278</v>
       </c>
       <c r="C10" t="n">
-        <v>3997.714008784879</v>
+        <v>96.22568518138632</v>
       </c>
       <c r="D10" t="n">
-        <v>6693.993945776569</v>
+        <v>28.76633779000134</v>
       </c>
       <c r="E10" t="n">
-        <v>1740.996382026485</v>
+        <v>49.30727696661152</v>
       </c>
       <c r="F10" t="n">
-        <v>8129.949699338094</v>
+        <v>8.751466774373274</v>
+      </c>
+      <c r="G10" t="n">
+        <v>48.41389881738622</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2.7745</v>
+        <v>1.8135</v>
       </c>
       <c r="B11" t="n">
-        <v>81.74021036489536</v>
+        <v>1.361322072466586</v>
       </c>
       <c r="C11" t="n">
-        <v>2040.759790934535</v>
+        <v>70.17440953349005</v>
       </c>
       <c r="D11" t="n">
-        <v>3476.183916282641</v>
+        <v>17.87420768093728</v>
       </c>
       <c r="E11" t="n">
-        <v>1010.669422610251</v>
+        <v>29.94173115285847</v>
       </c>
       <c r="F11" t="n">
-        <v>4584.93101770086</v>
+        <v>5.8777414675591</v>
+      </c>
+      <c r="G11" t="n">
+        <v>34.1922582240187</v>
       </c>
     </row>
   </sheetData>

--- a/aligned.xlsx
+++ b/aligned.xlsx
@@ -470,22 +470,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12.21101387668025</v>
+        <v>18233.47736896032</v>
       </c>
       <c r="C2" t="n">
-        <v>159.9583738044581</v>
+        <v>261109.543510504</v>
       </c>
       <c r="D2" t="n">
-        <v>145.759803339482</v>
+        <v>175630.4757692154</v>
       </c>
       <c r="E2" t="n">
-        <v>247.9251519432211</v>
+        <v>299028.3598113</v>
       </c>
       <c r="F2" t="n">
-        <v>38.22696172506139</v>
+        <v>38278.60079255436</v>
       </c>
       <c r="G2" t="n">
-        <v>130.1872620167249</v>
+        <v>159179.6151890083</v>
       </c>
     </row>
     <row r="3">
@@ -493,22 +493,22 @@
         <v>0.2015</v>
       </c>
       <c r="B3" t="n">
-        <v>15.94287236113902</v>
+        <v>17630.50468831427</v>
       </c>
       <c r="C3" t="n">
-        <v>209.8273032595552</v>
+        <v>255855.372314832</v>
       </c>
       <c r="D3" t="n">
-        <v>160.946422111699</v>
+        <v>170368.9684616729</v>
       </c>
       <c r="E3" t="n">
-        <v>273.8117638848835</v>
+        <v>290849.3761378219</v>
       </c>
       <c r="F3" t="n">
-        <v>37.24076451610355</v>
+        <v>37260.14861704777</v>
       </c>
       <c r="G3" t="n">
-        <v>146.3375685862185</v>
+        <v>158719.3753827651</v>
       </c>
     </row>
     <row r="4">
@@ -516,22 +516,22 @@
         <v>0.403</v>
       </c>
       <c r="B4" t="n">
-        <v>16.01289249425934</v>
+        <v>15937.20513296838</v>
       </c>
       <c r="C4" t="n">
-        <v>232.2420713895919</v>
+        <v>245592.1294321936</v>
       </c>
       <c r="D4" t="n">
-        <v>160.2019482270446</v>
+        <v>160436.4323490965</v>
       </c>
       <c r="E4" t="n">
-        <v>266.8232819346197</v>
+        <v>267741.872480978</v>
       </c>
       <c r="F4" t="n">
-        <v>35.35064294353376</v>
+        <v>35353.17910560488</v>
       </c>
       <c r="G4" t="n">
-        <v>145.5711408250891</v>
+        <v>148615.8841201731</v>
       </c>
     </row>
     <row r="5">
@@ -539,22 +539,22 @@
         <v>0.6045</v>
       </c>
       <c r="B5" t="n">
-        <v>14.1728147989769</v>
+        <v>13483.15406657815</v>
       </c>
       <c r="C5" t="n">
-        <v>231.847406715758</v>
+        <v>228249.9824320799</v>
       </c>
       <c r="D5" t="n">
-        <v>139.8963887663711</v>
+        <v>136965.4420153598</v>
       </c>
       <c r="E5" t="n">
-        <v>236.4770463056933</v>
+        <v>231256.753220334</v>
       </c>
       <c r="F5" t="n">
-        <v>31.41299862151702</v>
+        <v>31408.72373268611</v>
       </c>
       <c r="G5" t="n">
-        <v>135.9412858492883</v>
+        <v>134169.9775236085</v>
       </c>
     </row>
     <row r="6">
@@ -562,22 +562,22 @@
         <v>0.806</v>
       </c>
       <c r="B6" t="n">
-        <v>11.38055463533234</v>
+        <v>10676.51633987303</v>
       </c>
       <c r="C6" t="n">
-        <v>212.4863095839963</v>
+        <v>201151.4217327783</v>
       </c>
       <c r="D6" t="n">
-        <v>117.2023352813611</v>
+        <v>113543.9462207303</v>
       </c>
       <c r="E6" t="n">
-        <v>198.2008842201856</v>
+        <v>191707.0509245991</v>
       </c>
       <c r="F6" t="n">
-        <v>26.49417358710955</v>
+        <v>26487.65197806707</v>
       </c>
       <c r="G6" t="n">
-        <v>121.6626366487313</v>
+        <v>117898.6086931204</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         <v>1.0075</v>
       </c>
       <c r="B7" t="n">
-        <v>8.360234556651175</v>
+        <v>7916.602942357626</v>
       </c>
       <c r="C7" t="n">
-        <v>185.2359609983585</v>
+        <v>172534.5613777325</v>
       </c>
       <c r="D7" t="n">
-        <v>91.32741218562043</v>
+        <v>88478.61116980361</v>
       </c>
       <c r="E7" t="n">
-        <v>157.2088416511988</v>
+        <v>151769.9975282654</v>
       </c>
       <c r="F7" t="n">
-        <v>21.42435278934765</v>
+        <v>21418.91850555521</v>
       </c>
       <c r="G7" t="n">
-        <v>104.0243980599022</v>
+        <v>100215.1256007249</v>
       </c>
     </row>
     <row r="8">
@@ -608,22 +608,22 @@
         <v>1.209</v>
       </c>
       <c r="B8" t="n">
-        <v>5.64194417360033</v>
+        <v>5503.967205797224</v>
       </c>
       <c r="C8" t="n">
-        <v>154.7829156001911</v>
+        <v>143327.4581050132</v>
       </c>
       <c r="D8" t="n">
-        <v>66.04928816684884</v>
+        <v>64476.35634387325</v>
       </c>
       <c r="E8" t="n">
-        <v>113.7847043672635</v>
+        <v>111005.9194312746</v>
       </c>
       <c r="F8" t="n">
-        <v>16.74058245734086</v>
+        <v>16735.83707584627</v>
       </c>
       <c r="G8" t="n">
-        <v>83.327889583184</v>
+        <v>80290.65759457108</v>
       </c>
     </row>
     <row r="9">
@@ -631,22 +631,22 @@
         <v>1.4105</v>
       </c>
       <c r="B9" t="n">
-        <v>3.513065511582063</v>
+        <v>3600.781761053361</v>
       </c>
       <c r="C9" t="n">
-        <v>125.2082246551783</v>
+        <v>116328.1529015291</v>
       </c>
       <c r="D9" t="n">
-        <v>45.74081887298403</v>
+        <v>45510.70051283158</v>
       </c>
       <c r="E9" t="n">
-        <v>76.60863904782903</v>
+        <v>75810.41065530952</v>
       </c>
       <c r="F9" t="n">
-        <v>12.53652444565592</v>
+        <v>12534.43478004382</v>
       </c>
       <c r="G9" t="n">
-        <v>64.95158945530336</v>
+        <v>62793.35339674793</v>
       </c>
     </row>
     <row r="10">
@@ -654,22 +654,22 @@
         <v>1.612</v>
       </c>
       <c r="B10" t="n">
-        <v>2.00716841768278</v>
+        <v>2196.828328115707</v>
       </c>
       <c r="C10" t="n">
-        <v>96.22568518138632</v>
+        <v>91589.24554495644</v>
       </c>
       <c r="D10" t="n">
-        <v>28.76633779000134</v>
+        <v>29361.8209717437</v>
       </c>
       <c r="E10" t="n">
-        <v>49.30727696661152</v>
+        <v>50193.38770532128</v>
       </c>
       <c r="F10" t="n">
-        <v>8.751466774373274</v>
+        <v>8751.23538438821</v>
       </c>
       <c r="G10" t="n">
-        <v>48.41389881738622</v>
+        <v>47554.38299006169</v>
       </c>
     </row>
     <row r="11">
@@ -677,22 +677,22 @@
         <v>1.8135</v>
       </c>
       <c r="B11" t="n">
-        <v>1.361322072466586</v>
+        <v>1679.437490705463</v>
       </c>
       <c r="C11" t="n">
-        <v>70.17440953349005</v>
+        <v>68834.51949894262</v>
       </c>
       <c r="D11" t="n">
-        <v>17.87420768093728</v>
+        <v>18879.26125146738</v>
       </c>
       <c r="E11" t="n">
-        <v>29.94173115285847</v>
+        <v>31461.14424519001</v>
       </c>
       <c r="F11" t="n">
-        <v>5.8777414675591</v>
+        <v>5878.793765161381</v>
       </c>
       <c r="G11" t="n">
-        <v>34.1922582240187</v>
+        <v>34231.90237042509</v>
       </c>
     </row>
   </sheetData>
